--- a/data/trans_orig/P41C_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P41C_R-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dificultades para tener un embarazo en 2023</t>
+          <t>Población con dificultades para tener un embarazo en 2023 (tasa de respuesta: 87,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19343</t>
+          <t>17948</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>663</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5597</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21029</t>
+          <t>21744</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>127749</t>
+          <t>129144</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>144755</t>
+          <t>144964</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>153520</t>
+          <t>153242</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>158239</t>
+          <t>158176</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>284902</t>
+          <t>284187</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>302035</t>
+          <t>302214</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>869</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17777</t>
+          <t>17573</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7183</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19164</t>
+          <t>18631</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32376</t>
+          <t>32958</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>474160</t>
+          <t>474364</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>491299</t>
+          <t>491068</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>226889</t>
+          <t>227422</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>238870</t>
+          <t>238902</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>705614</t>
+          <t>705032</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>732002</t>
+          <t>731681</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10182</t>
+          <t>10457</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10058</t>
+          <t>10066</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15859</t>
+          <t>17727</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74357</t>
+          <t>74082</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83098</t>
+          <t>83315</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>98820</t>
+          <t>98812</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>106982</t>
+          <t>106870</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>177558</t>
+          <t>175690</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>188828</t>
+          <t>188730</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3679</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15662</t>
+          <t>16202</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5766</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16994</t>
+          <t>16581</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12358</t>
+          <t>11638</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27884</t>
+          <t>27490</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>140189</t>
+          <t>139649</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>152172</t>
+          <t>151899</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>164515</t>
+          <t>164928</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>175743</t>
+          <t>175806</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>309475</t>
+          <t>309869</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>325001</t>
+          <t>325721</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,55%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10962</t>
+          <t>10115</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44316</t>
+          <t>44032</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21071</t>
+          <t>21409</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39850</t>
+          <t>40083</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32890</t>
+          <t>35191</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75740</t>
+          <t>75386</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>835103</t>
+          <t>835387</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>868457</t>
+          <t>869304</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>655429</t>
+          <t>655196</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>674208</t>
+          <t>673870</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1498957</t>
+          <t>1499311</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1541807</t>
+          <t>1539506</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P41C_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P41C_R-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>7647</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17948</t>
+          <t>21653</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>557</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5597</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9162</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3717</t>
+          <t>3683</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21744</t>
+          <t>25029</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>140148</t>
+          <t>145787</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>129144</t>
+          <t>131781</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>144964</t>
+          <t>150852</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>156621</t>
+          <t>167178</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>153242</t>
+          <t>163922</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>158176</t>
+          <t>168861</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>296769</t>
+          <t>312965</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>284187</t>
+          <t>297823</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>302214</t>
+          <t>319169</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>147092</t>
+          <t>153434</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>147092</t>
+          <t>153434</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>147092</t>
+          <t>153434</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>158839</t>
+          <t>169418</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>158839</t>
+          <t>169418</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>158839</t>
+          <t>169418</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>305931</t>
+          <t>322852</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>305931</t>
+          <t>322852</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>305931</t>
+          <t>322852</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6547</t>
+          <t>6527</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>2876</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17573</t>
+          <t>13879</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12074</t>
+          <t>14042</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18631</t>
+          <t>22035</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>18621</t>
+          <t>20570</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>13041</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32958</t>
+          <t>29612</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>485390</t>
+          <t>269864</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>474364</t>
+          <t>262512</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>491068</t>
+          <t>273515</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>233979</t>
+          <t>257747</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>227422</t>
+          <t>249754</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>238902</t>
+          <t>263441</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>719369</t>
+          <t>527609</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>705032</t>
+          <t>518567</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>731681</t>
+          <t>535138</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>491937</t>
+          <t>276391</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>491937</t>
+          <t>276391</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>491937</t>
+          <t>276391</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>246053</t>
+          <t>271789</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>246053</t>
+          <t>271789</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>246053</t>
+          <t>271789</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>737990</t>
+          <t>548179</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>737990</t>
+          <t>548179</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>737990</t>
+          <t>548179</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>2180</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10457</t>
+          <t>12320</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10066</t>
+          <t>11067</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,22 +1481,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>10627</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4687</t>
+          <t>5524</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17727</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80177</t>
+          <t>90196</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74082</t>
+          <t>83523</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83315</t>
+          <t>93663</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>104035</t>
+          <t>127149</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>98812</t>
+          <t>121062</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>106870</t>
+          <t>130262</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,27 +1594,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>184213</t>
+          <t>217345</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>175690</t>
+          <t>209566</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>188730</t>
+          <t>222448</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>84539</t>
+          <t>95843</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>84539</t>
+          <t>95843</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84539</t>
+          <t>95843</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>108878</t>
+          <t>132129</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>108878</t>
+          <t>132129</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>108878</t>
+          <t>132129</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>193417</t>
+          <t>227972</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>193417</t>
+          <t>227972</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>193417</t>
+          <t>227972</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8639</t>
+          <t>8734</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16202</t>
+          <t>16910</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>10507</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16581</t>
+          <t>17265</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>18942</t>
+          <t>19241</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11638</t>
+          <t>12235</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27490</t>
+          <t>28186</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>147212</t>
+          <t>161353</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>139649</t>
+          <t>153177</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>151899</t>
+          <t>166141</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>171206</t>
+          <t>189754</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>164928</t>
+          <t>182996</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>175806</t>
+          <t>194355</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>318417</t>
+          <t>351107</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>309869</t>
+          <t>342162</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>325721</t>
+          <t>358113</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>155851</t>
+          <t>170087</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>155851</t>
+          <t>170087</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>155851</t>
+          <t>170087</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181509</t>
+          <t>200261</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181509</t>
+          <t>200261</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181509</t>
+          <t>200261</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>337359</t>
+          <t>370348</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>337359</t>
+          <t>370348</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>337359</t>
+          <t>370348</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>26491</t>
+          <t>28556</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10115</t>
+          <t>18345</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44032</t>
+          <t>45806</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>29437</t>
+          <t>31769</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21409</t>
+          <t>23090</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40083</t>
+          <t>42269</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>55929</t>
+          <t>60325</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35191</t>
+          <t>46801</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75386</t>
+          <t>79563</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>852928</t>
+          <t>667199</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>835387</t>
+          <t>649949</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>869304</t>
+          <t>677410</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>665842</t>
+          <t>741827</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>655196</t>
+          <t>731327</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>673870</t>
+          <t>750506</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1518768</t>
+          <t>1409027</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1499311</t>
+          <t>1389789</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1539506</t>
+          <t>1422551</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>879419</t>
+          <t>695755</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>879419</t>
+          <t>695755</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>879419</t>
+          <t>695755</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>695279</t>
+          <t>773596</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>695279</t>
+          <t>773596</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>695279</t>
+          <t>773596</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1574697</t>
+          <t>1469352</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1574697</t>
+          <t>1469352</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1574697</t>
+          <t>1469352</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
